--- a/MEME_OUTPUT/reverse_meme_out_3_motif6.xlsx
+++ b/MEME_OUTPUT/reverse_meme_out_3_motif6.xlsx
@@ -477,16 +477,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TTCC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>GGAA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CCTT</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>0.04</v>
+        <v>0.04018392642942823</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +506,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TCC</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>GGA</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CCT</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>0.2604</v>
+        <v>0.2604958016793283</v>
       </c>
     </row>
     <row r="4">
@@ -535,16 +535,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AG</t>
-        </is>
-      </c>
       <c r="G4" t="n">
-        <v>0.9166</v>
+        <v>0.9164334266293482</v>
       </c>
     </row>
     <row r="5">
@@ -564,16 +564,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AG</t>
-        </is>
-      </c>
       <c r="G5" t="n">
-        <v>0.9166</v>
+        <v>0.9164334266293482</v>
       </c>
     </row>
     <row r="6">
@@ -593,16 +593,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AG</t>
-        </is>
-      </c>
       <c r="G6" t="n">
-        <v>0.9928</v>
+        <v>0.9926029588164734</v>
       </c>
     </row>
     <row r="7">
@@ -622,16 +622,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>TG</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
       <c r="G7" t="n">
-        <v>0.998</v>
+        <v>0.9978008796481408</v>
       </c>
     </row>
     <row r="8">
@@ -651,16 +651,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>TC</t>
-        </is>
-      </c>
       <c r="G8" t="n">
-        <v>0.9992</v>
+        <v>0.9990003998400639</v>
       </c>
     </row>
     <row r="9">
@@ -680,16 +680,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
       <c r="G9" t="n">
-        <v>0.9998</v>
+        <v>0.9996001599360256</v>
       </c>
     </row>
     <row r="10">
@@ -709,16 +709,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
       <c r="G10" t="n">
-        <v>0.999</v>
+        <v>0.9988004798080767</v>
       </c>
     </row>
     <row r="11">
@@ -738,16 +738,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
       <c r="G11" t="n">
-        <v>0.9944</v>
+        <v>0.994202319072371</v>
       </c>
     </row>
   </sheetData>

--- a/MEME_OUTPUT/reverse_meme_out_3_motif6.xlsx
+++ b/MEME_OUTPUT/reverse_meme_out_3_motif6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TTCCGTATCTCGCAGGAA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TTCC</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>GGAA</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;GTATCTCGCA&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.04018392642942823</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TCCTTTCCGTATCTCGCAGGA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TCC</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>GGA</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;TTTCCGTATCTCGCA&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.2604958016793283</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>GATTC</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;T&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9164334266293482</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>GATTCCTTTC</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;TTCCTT&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.9164334266293482</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>GATTCCTTTCCGTATCTC</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;TTCCTTTCCGTATC&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9926029588164734</v>
       </c>
     </row>
@@ -622,15 +682,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>TGATTCCTTTCCGTATCTCGCA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;ATTCCTTTCCGTATCTCG&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9978008796481408</v>
       </c>
     </row>
@@ -651,15 +721,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>CTCGCAG</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;CGC&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.9990003998400639</v>
       </c>
     </row>
@@ -680,15 +760,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>TCTCGCAGGA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;TCGCAG&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.9996001599360256</v>
       </c>
     </row>
@@ -709,15 +799,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>TCGCAGGA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;GCAG&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.9988004798080767</v>
       </c>
     </row>
@@ -738,15 +838,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>TTTCCGTATCTCGCAGGAA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;TCCGTATCTCGCAGG&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.994202319072371</v>
       </c>
     </row>
